--- a/output/full_scan/batch_seq4_2026-07-06.xlsx
+++ b/output/full_scan/batch_seq4_2026-07-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O222"/>
+  <dimension ref="A1:O224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3317</v>
+        <v>3189</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>尼克森</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>469.8606331826679</v>
+        <v>470.4707398532906</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>105.5</v>
+        <v>763</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>70.06759620860161</v>
+        <v>52.9445559199381</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>37.9668133226434</v>
+        <v>27.551319437244</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.229466384598829</v>
+        <v>0.1537366847308928</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.9454819109149524</v>
+        <v>-0.981163998437161</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>3413</v>
+        <v>3317</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>尼克森</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>469.7445329684896</v>
+        <v>469.8606331826679</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>325.5</v>
+        <v>105.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.79827039696466</v>
+        <v>70.06759620860161</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.21401028144196</v>
+        <v>37.9668133226434</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6782838433183929</v>
+        <v>1.229466384598829</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.721760627494774</v>
+        <v>0.9454819109149524</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>3260</v>
+        <v>3413</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>462.3867926268711</v>
+        <v>469.7445329684896</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>410.5</v>
+        <v>325.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,49 +6170,49 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>49.00778671047976</v>
+        <v>53.79827039696466</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6.539658220528128</v>
+        <v>9.21401028144196</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6334378618934169</v>
+        <v>0.6782838433183929</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2385177300916394</v>
+        <v>1.721760627494774</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4178</v>
+        <v>3260</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>永笙-KY</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>458.0358281279096</v>
+        <v>462.3867926268711</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.6</v>
+        <v>410.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,49 +6223,49 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.84421275916499</v>
+        <v>49.00778671047976</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>36.16013160105637</v>
+        <v>6.539658220528128</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.324441598720806</v>
+        <v>0.6334378618934169</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.2195975731419469</v>
+        <v>-0.2385177300916394</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>3689</v>
+        <v>4178</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>455.6361193260027</v>
+        <v>458.0358281279096</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>123</v>
+        <v>18.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.9856342755404</v>
+        <v>52.84421275916499</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.23722710456738</v>
+        <v>36.16013160105637</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.511929073269951</v>
+        <v>1.324441598720806</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.9153526107543912</v>
+        <v>0.2195975731419469</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>3390</v>
+        <v>3689</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>旭軟</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>453.3841119679498</v>
+        <v>455.6361193260027</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>27.95</v>
+        <v>123</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.43421638107654</v>
+        <v>50.9856342755404</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.96938635058876</v>
+        <v>14.23722710456738</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.396860622604461</v>
+        <v>0.511929073269951</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1055216188506356</v>
+        <v>0.9153526107543912</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3346</v>
+        <v>3390</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>麗清</t>
+          <t>旭軟</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>449.6740000437987</v>
+        <v>453.3841119679498</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>28.25</v>
+        <v>27.95</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>65.85182741004125</v>
+        <v>50.43421638107654</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>31.40678051218238</v>
+        <v>11.96938635058876</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.367400004379869</v>
+        <v>0.396860622604461</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2255587955932489</v>
+        <v>-0.1055216188506356</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3288</v>
+        <v>3346</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>點晶</t>
+          <t>麗清</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>447.4657149560479</v>
+        <v>449.6740000437987</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>20.2</v>
+        <v>28.25</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.42035939126358</v>
+        <v>65.85182741004125</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.40993100579732</v>
+        <v>31.40678051218238</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2116393207065944</v>
+        <v>1.367400004379869</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.5620693575585819</v>
+        <v>0.2255587955932489</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3357</v>
+        <v>3288</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>點晶</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>446.9278470263188</v>
+        <v>447.4657149560479</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>284</v>
+        <v>20.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.64410550263331</v>
+        <v>48.42035939126358</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>29.99940701764359</v>
+        <v>18.40993100579732</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3396427299330077</v>
+        <v>0.2116393207065944</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-6.974893448457575</v>
+        <v>-0.5620693575585819</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3533</v>
+        <v>3357</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>臺慶科</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>440.4883190127687</v>
+        <v>446.9278470263188</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>2125</v>
+        <v>284</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.60259995771233</v>
+        <v>47.64410550263331</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>25.59670920208496</v>
+        <v>29.99940701764359</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.100551738094077</v>
+        <v>0.3396427299330077</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.244218310545961</v>
+        <v>-6.974893448457575</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3504</v>
+        <v>3450</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>439.4822363453575</v>
+        <v>444.5756250167278</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>78.2</v>
+        <v>520</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>47.19254482447012</v>
+        <v>51.73100714840018</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>29.54204276572941</v>
+        <v>27.98352382750486</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2061214154503942</v>
+        <v>0.1537942736675988</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-1.32996066537703</v>
+        <v>-7.698327819701518</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>3520</v>
+        <v>3533</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>華盈</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>438.0768828331714</v>
+        <v>440.4883190127687</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>17.8</v>
+        <v>2125</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>58.57471849113807</v>
+        <v>38.60259995771233</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>27.39314744983432</v>
+        <v>25.59670920208496</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5056732305527947</v>
+        <v>1.100551738094077</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1328974420826783</v>
+        <v>-2.244218310545961</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>4119</v>
+        <v>3504</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>436.4641956229377</v>
+        <v>439.4822363453575</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>45.35</v>
+        <v>78.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>60.49849958198935</v>
+        <v>47.19254482447012</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.76041832651707</v>
+        <v>29.54204276572941</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2903500616710064</v>
+        <v>0.2061214154503942</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.2977775584861646</v>
+        <v>-1.32996066537703</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3587</v>
+        <v>3520</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>華盈</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>431.2692759838615</v>
+        <v>438.0768828331714</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>300.5</v>
+        <v>17.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>48.89109731980045</v>
+        <v>58.57471849113807</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.55016784835917</v>
+        <v>27.39314744983432</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7170917435689027</v>
+        <v>0.5056732305527947</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>1.572717252307536</v>
+        <v>0.1328974420826783</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3555</v>
+        <v>4119</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>博士旺</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>430.7392275180696</v>
+        <v>436.4641956229377</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>188</v>
+        <v>45.35</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.96090844190941</v>
+        <v>60.49849958198935</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9.268814508439023</v>
+        <v>23.76041832651707</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2346386026494248</v>
+        <v>0.2903500616710064</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0199371969283426</v>
+        <v>0.2977775584861646</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>3521</v>
+        <v>3587</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>鴻翊</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>425.2566898996054</v>
+        <v>431.2692759838615</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13</v>
+        <v>300.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>57.21498948043055</v>
+        <v>48.89109731980045</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.96669562406264</v>
+        <v>13.55016784835917</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.205603530559027</v>
+        <v>0.7170917435689027</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1189532442614986</v>
+        <v>1.572717252307536</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3545</v>
+        <v>3555</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>博士旺</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>423.6395924323279</v>
+        <v>430.7392275180696</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>58.5</v>
+        <v>188</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>55.00596794376883</v>
+        <v>43.96090844190941</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.97620637734452</v>
+        <v>9.268814508439023</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.392593550688735</v>
+        <v>0.2346386026494248</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0117819378145347</v>
+        <v>0.0199371969283426</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>4142</v>
+        <v>3521</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>國光生</t>
+          <t>鴻翊</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>418.7261191109485</v>
+        <v>425.2566898996054</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>17.95</v>
+        <v>13</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>59.24985313207653</v>
+        <v>57.21498948043055</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.79769112309224</v>
+        <v>19.96669562406264</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.069715435181403</v>
+        <v>1.205603530559027</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0712976021781758</v>
+        <v>0.1189532442614986</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3563</v>
+        <v>3545</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>418.0243226559302</v>
+        <v>423.6395924323279</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>777</v>
+        <v>58.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>53.50424591785275</v>
+        <v>55.00596794376883</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>23.29594880169421</v>
+        <v>17.97620637734452</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.335720935160525</v>
+        <v>1.392593550688735</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>14.6193236512572</v>
+        <v>-0.0117819378145347</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>3628</v>
+        <v>4142</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>盈正</t>
+          <t>國光生</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>416.7776541628693</v>
+        <v>418.7261191109485</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>60.65886974362815</v>
+        <v>59.24985313207653</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>23.15676207577312</v>
+        <v>10.79769112309224</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.487838724090492</v>
+        <v>1.069715435181403</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.5954990973626719</v>
+        <v>0.0712976021781758</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3528</v>
+        <v>3563</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>安馳</t>
+          <t>牧德</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>414.3735544992811</v>
+        <v>418.0243226559302</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>100.5</v>
+        <v>777</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>44.64117328662744</v>
+        <v>53.50424591785275</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>21.28849024607446</v>
+        <v>23.29594880169421</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7767265624162284</v>
+        <v>1.335720935160525</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-2.475894684075254</v>
+        <v>14.6193236512572</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3583</v>
+        <v>3628</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>盈正</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>413.8717215099689</v>
+        <v>416.7776541628693</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>860</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>51.00822619327888</v>
+        <v>60.65886974362815</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>14.76553551763057</v>
+        <v>23.15676207577312</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.8290035015914224</v>
+        <v>1.487838724090492</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.1246872869243951</v>
+        <v>0.5954990973626719</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3652</v>
+        <v>3528</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>精聯</t>
+          <t>安馳</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>409.5205106453692</v>
+        <v>414.3735544992811</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>37.3</v>
+        <v>100.5</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>52.33321434433535</v>
+        <v>44.64117328662744</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>38.27810330735846</v>
+        <v>21.28849024607446</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.1717540680710885</v>
+        <v>0.7767265624162284</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.4162852033727025</v>
+        <v>-2.475894684075254</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>3294</v>
+        <v>3583</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>407.9723227836364</v>
+        <v>413.8717215099689</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>39.4</v>
+        <v>860</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>53.97910078906114</v>
+        <v>51.00822619327888</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>19.57055123982012</v>
+        <v>14.76553551763057</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2.090019265100294</v>
+        <v>0.8290035015914224</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0558394405111268</v>
+        <v>0.1246872869243951</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>3669</v>
+        <v>3652</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>圓展</t>
+          <t>精聯</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>404.0589527884773</v>
+        <v>409.5205106453692</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>36.35</v>
+        <v>37.3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>51.7373657041229</v>
+        <v>52.33321434433535</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>21.28382304314352</v>
+        <v>38.27810330735846</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.016981437680435</v>
+        <v>0.1717540680710885</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1918819442887216</v>
+        <v>-0.4162852033727025</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3466</v>
+        <v>3294</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>英濟</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>400.5163867562443</v>
+        <v>407.9723227836364</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>34</v>
+        <v>39.4</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>55.29423941287215</v>
+        <v>53.97910078906114</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>16.76753212177385</v>
+        <v>19.57055123982012</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.683662997162236</v>
+        <v>2.090019265100294</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.475539873858491</v>
+        <v>-0.0558394405111268</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>3552</v>
+        <v>3669</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>同致</t>
+          <t>圓展</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>394.952203900816</v>
+        <v>404.0589527884773</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>49.05</v>
+        <v>36.35</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>44.34663698757618</v>
+        <v>51.7373657041229</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>12.50940828313482</v>
+        <v>21.28382304314352</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.143354301104258</v>
+        <v>1.016981437680435</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0079625991894576</v>
+        <v>0.1918819442887216</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>3380</v>
+        <v>3466</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>明泰</t>
+          <t>德晉</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>386.8856741128294</v>
+        <v>400.5163867562443</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>52.69628543158564</v>
+        <v>55.29423941287215</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>14.972140573483</v>
+        <v>16.76753212177385</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.10208947983179</v>
+        <v>0.683662997162236</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.1335178569651022</v>
+        <v>0.475539873858491</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3229</v>
+        <v>3552</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>晟鈦</t>
+          <t>同致</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>381.1668778266935</v>
+        <v>394.952203900816</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>41.7</v>
+        <v>49.05</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>46.45078698645253</v>
+        <v>44.34663698757618</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>25.76838478508886</v>
+        <v>12.50940828313482</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.5069432869649382</v>
+        <v>1.143354301104258</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.5928740515689725</v>
+        <v>0.0079625991894576</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3266</v>
+        <v>3380</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>昇陽</t>
+          <t>明泰</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>379.6972393666352</v>
+        <v>386.8856741128294</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>13.55</v>
+        <v>35.4</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>54.57589759564623</v>
+        <v>52.69628543158564</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>14.19434050231327</v>
+        <v>14.972140573483</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.5029929270289495</v>
+        <v>1.10208947983179</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0044563157731765</v>
+        <v>0.1335178569651022</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3645</v>
+        <v>3229</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>晟鈦</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>377.7898705060959</v>
+        <v>381.1668778266935</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>91</v>
+        <v>41.7</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>44.69113728237764</v>
+        <v>46.45078698645253</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.20773365613169</v>
+        <v>25.76838478508886</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.7595997621602081</v>
+        <v>0.5069432869649382</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.2614013817842013</v>
+        <v>-0.5928740515689725</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3313</v>
+        <v>3266</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>斐成</t>
+          <t>昇陽</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>368.3796779070589</v>
+        <v>379.6972393666352</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>12.2</v>
+        <v>13.55</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>58.11711578636088</v>
+        <v>54.57589759564623</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>21.03389525567211</v>
+        <v>14.19434050231327</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.621744640736082</v>
+        <v>0.5029929270289495</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.0713613518779815</v>
+        <v>-0.0044563157731765</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3455</v>
+        <v>3645</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>由田</t>
+          <t>達邁</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>365.4851953654576</v>
+        <v>377.7898705060959</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>246.5</v>
+        <v>91</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>51.86253586328314</v>
+        <v>44.69113728237764</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>16.45530801410213</v>
+        <v>12.20773365613169</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.9788485205354748</v>
+        <v>0.7595997621602081</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>1.996220743459148</v>
+        <v>0.2614013817842013</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3526</v>
+        <v>3313</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>凡甲</t>
+          <t>斐成</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>365.1893795563759</v>
+        <v>368.3796779070589</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>330.5</v>
+        <v>12.2</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>49.34395315946124</v>
+        <v>58.11711578636088</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>20.24609619393299</v>
+        <v>21.03389525567211</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.7043217211212396</v>
+        <v>1.621744640736082</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>2.710032609335141</v>
+        <v>0.0713613518779815</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3332</v>
+        <v>3455</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>幸康</t>
+          <t>由田</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>362.9670707267005</v>
+        <v>365.4851953654576</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>246.5</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>52.40108837961439</v>
+        <v>51.86253586328314</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>27.53067349268053</v>
+        <v>16.45530801410213</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>1.567858118110349</v>
+        <v>0.9788485205354748</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-1.068624950192573</v>
+        <v>1.996220743459148</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3653</v>
+        <v>3526</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>362.1512803946224</v>
+        <v>365.1893795563759</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3320</v>
+        <v>330.5</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>39.74426066777914</v>
+        <v>49.34395315946124</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>20.25066256183026</v>
+        <v>20.24609619393299</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.4779183952755029</v>
+        <v>0.7043217211212396</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-27.60898943174338</v>
+        <v>2.710032609335141</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3311</v>
+        <v>3332</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>幸康</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>360.8062210091132</v>
+        <v>362.9670707267005</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>38.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>54.93831890484301</v>
+        <v>52.40108837961439</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>20.51481099221637</v>
+        <v>27.53067349268053</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.3532302778554536</v>
+        <v>1.567858118110349</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.248381831267651</v>
+        <v>-1.068624950192573</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3623</v>
+        <v>3653</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>富晶通</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>357.6284148100544</v>
+        <v>362.1512803946224</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>25.2</v>
+        <v>3320</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>59.17820060862962</v>
+        <v>39.74426066777914</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>17.3134155324265</v>
+        <v>20.25066256183026</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.7148219142102193</v>
+        <v>0.4779183952755029</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.1349902186837455</v>
+        <v>-27.60898943174338</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>3485</v>
+        <v>3311</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>敘豐</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>354.4491536708308</v>
+        <v>360.8062210091132</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>311.5</v>
+        <v>38.6</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>51.15245687462632</v>
+        <v>54.93831890484301</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>12.44622265503245</v>
+        <v>20.51481099221637</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.249571325706977</v>
+        <v>0.3532302778554536</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>1.210497923990321</v>
+        <v>-0.248381831267651</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3191</v>
+        <v>3623</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>雲嘉南</t>
+          <t>富晶通</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>353.6091980564256</v>
+        <v>357.6284148100544</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>18.9</v>
+        <v>25.2</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>49.01723520607467</v>
+        <v>59.17820060862962</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>10.05038724335401</v>
+        <v>17.3134155324265</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.6630275294448451</v>
+        <v>0.7148219142102193</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.243870422775986</v>
+        <v>0.1349902186837455</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3622</v>
+        <v>3485</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>敘豐</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>352.1028290581806</v>
+        <v>354.4491536708308</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>57.9</v>
+        <v>311.5</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>54.40428248053981</v>
+        <v>51.15245687462632</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>14.08501205142668</v>
+        <v>12.44622265503245</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.9095914868569585</v>
+        <v>1.249571325706977</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.262019250091582</v>
+        <v>1.210497923990321</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3443</v>
+        <v>3191</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>雲嘉南</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>351.8706448154745</v>
+        <v>353.6091980564256</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>4605</v>
+        <v>18.9</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>47.93983117722255</v>
+        <v>49.01723520607467</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>16.74167132548826</v>
+        <v>10.05038724335401</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.043275357120717</v>
+        <v>0.6630275294448451</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>10.52139093471874</v>
+        <v>-0.243870422775986</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>3491</v>
+        <v>3622</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>洋華</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>345.2504746859333</v>
+        <v>352.1028290581806</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>1300</v>
+        <v>57.9</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,49 +8290,49 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>37.26182803482045</v>
+        <v>54.40428248053981</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>29.21704066939926</v>
+        <v>14.08501205142668</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.6110145370275127</v>
+        <v>0.9095914868569585</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-12.31047936480356</v>
+        <v>0.262019250091582</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>3715</v>
+        <v>3443</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>345.0767545982921</v>
+        <v>351.8706448154745</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>165</v>
+        <v>4605</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>44.00648647671949</v>
+        <v>47.93983117722255</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>12.70050475581586</v>
+        <v>16.74167132548826</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.013721842132852</v>
+        <v>1.043275357120717</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.6684508041551877</v>
+        <v>10.52139093471874</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8371,21 +8371,21 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>單井</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>343.9034921502328</v>
+        <v>345.2504746859333</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>33.7</v>
+        <v>1300</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,49 +8396,49 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>50.96377819914336</v>
+        <v>37.26182803482045</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20.53598276712032</v>
+        <v>29.21704066939926</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.9370983214368632</v>
+        <v>0.6110145370275127</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.190912051079431</v>
+        <v>-12.31047936480356</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>3209</v>
+        <v>3715</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>343.4144746741056</v>
+        <v>345.0767545982921</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>60.4</v>
+        <v>165</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>43.53476872696729</v>
+        <v>44.00648647671949</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>29.59884698105157</v>
+        <v>12.70050475581586</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.4493752314359545</v>
+        <v>1.013721842132852</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.2824916812757316</v>
+        <v>-0.6684508041551877</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>3363</v>
+        <v>3490</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>單井</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>342.2031428431664</v>
+        <v>343.9034921502328</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>574</v>
+        <v>33.7</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,13 +8502,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>35.91210576305409</v>
+        <v>50.96377819914336</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>33.73753090256356</v>
+        <v>20.53598276712032</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.773387206818483</v>
+        <v>0.9370983214368632</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-9.190995007580746</v>
+        <v>0.190912051079431</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3135</v>
+        <v>3209</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>全科</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>337.5966235253877</v>
+        <v>343.4144746741056</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>183</v>
+        <v>60.4</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,13 +8555,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>44.06068132664608</v>
+        <v>43.53476872696729</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>20.14680030618499</v>
+        <v>29.59884698105157</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.5273562206754852</v>
+        <v>0.4493752314359545</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-2.25685135864254</v>
+        <v>-0.2824916812757316</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8583,21 +8583,21 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>3714</v>
+        <v>3363</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>331.3907118403125</v>
+        <v>342.2031428431664</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>574</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,13 +8608,13 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46.2540307010548</v>
+        <v>35.91210576305409</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>11.69357094672055</v>
+        <v>33.73753090256356</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.4901981825111718</v>
+        <v>1.773387206818483</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.3717795111640842</v>
+        <v>-9.190995007580746</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3437</v>
+        <v>3135</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>榮創</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>330.8090834344782</v>
+        <v>337.5966235253877</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>21.75</v>
+        <v>183</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45.93603260040403</v>
+        <v>44.06068132664608</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>10.1811998538437</v>
+        <v>20.14680030618499</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5043253761254919</v>
+        <v>0.5273562206754852</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0505085733335902</v>
+        <v>-2.25685135864254</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>3581</v>
+        <v>3714</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>博磊</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>330.3822245238918</v>
+        <v>331.3907118403125</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>140</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,13 +8714,13 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>39.15778221111218</v>
+        <v>46.2540307010548</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>24.65173980277204</v>
+        <v>11.69357094672055</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.806025621705066</v>
+        <v>0.4901981825111718</v>
       </c>
       <c r="K156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.4495573431331277</v>
+        <v>-0.3717795111640842</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>3217</v>
+        <v>3437</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>榮創</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>329.9856412262982</v>
+        <v>330.8090834344782</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>178.5</v>
+        <v>21.75</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,13 +8767,13 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>49.67730585536036</v>
+        <v>45.93603260040403</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>14.61002217694913</v>
+        <v>10.1811998538437</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.5952834120302818</v>
+        <v>0.5043253761254919</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.4345875848094137</v>
+        <v>0.0505085733335902</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>3548</v>
+        <v>3581</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>兆利</t>
+          <t>博磊</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>327.6174102795015</v>
+        <v>330.3822245238918</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>87.5</v>
+        <v>140</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>45.2290161763365</v>
+        <v>39.15778221111218</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>12.92220569933602</v>
+        <v>24.65173980277204</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.5601216744687317</v>
+        <v>0.806025621705066</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8838,31 +8838,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.1343895449914898</v>
+        <v>-0.4495573431331277</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3691</v>
+        <v>3217</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>碩禾</t>
+          <t>優群</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>324.0390623576812</v>
+        <v>329.9856412262982</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>153.5</v>
+        <v>178.5</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,13 +8873,13 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>50.52116917784202</v>
+        <v>49.67730585536036</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>18.51111759102547</v>
+        <v>14.61002217694913</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.3622376086711288</v>
+        <v>0.5952834120302818</v>
       </c>
       <c r="K159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-1.140251986130179</v>
+        <v>0.4345875848094137</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>3178</v>
+        <v>3548</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>公準</t>
+          <t>兆利</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>322.9332442855489</v>
+        <v>327.6174102795015</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>68</v>
+        <v>87.5</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,16 +8926,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>54.03285657304509</v>
+        <v>45.2290161763365</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>16.81674812162576</v>
+        <v>12.92220569933602</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.7692806274542942</v>
+        <v>0.5601216744687317</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.3180836818826035</v>
+        <v>0.1343895449914898</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>3297</v>
+        <v>3691</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>杭特</t>
+          <t>碩禾</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>322.5740575567547</v>
+        <v>324.0390623576812</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>32</v>
+        <v>153.5</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,13 +8979,13 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>52.51716741360345</v>
+        <v>50.52116917784202</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14.50158220805915</v>
+        <v>18.51111759102547</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.7278659609144197</v>
+        <v>0.3622376086711288</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.0432239528855824</v>
+        <v>-1.140251986130179</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>3673</v>
+        <v>3178</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>公準</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>317.0356812813155</v>
+        <v>322.9332442855489</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>81.2</v>
+        <v>68</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,16 +9032,16 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>51.24198633105856</v>
+        <v>54.03285657304509</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>17.65032438528901</v>
+        <v>16.81674812162576</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.56060876400431</v>
+        <v>0.7692806274542942</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.6876250606428151</v>
+        <v>0.3180836818826035</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>3444</v>
+        <v>3297</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>利機</t>
+          <t>杭特</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>311.2889462553701</v>
+        <v>322.5740575567547</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>32</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>44.32065257483442</v>
+        <v>52.51716741360345</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>21.54255541047975</v>
+        <v>14.50158220805915</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.8717633566329619</v>
+        <v>0.7278659609144197</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.6026476682059669</v>
+        <v>0.0432239528855824</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>3541</v>
+        <v>3673</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>西柏</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>310.2217723941928</v>
+        <v>317.0356812813155</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>22.3</v>
+        <v>81.2</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,13 +9138,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>54.86737080601456</v>
+        <v>51.24198633105856</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>25.04341006107894</v>
+        <v>17.65032438528901</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.8225951434511225</v>
+        <v>0.56060876400431</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1020485842383657</v>
+        <v>-0.6876250606428151</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>3224</v>
+        <v>3444</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>三顧</t>
+          <t>利機</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>306.1729769676325</v>
+        <v>311.2889462553701</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>38.4</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>48.88812647579092</v>
+        <v>44.32065257483442</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>13.88592684037264</v>
+        <v>21.54255541047975</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.3726678371602096</v>
+        <v>0.8717633566329619</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.2486498962134201</v>
+        <v>-0.6026476682059669</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>3680</v>
+        <v>3541</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>西柏</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>298.9365022685526</v>
+        <v>310.2217723941928</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>535</v>
+        <v>22.3</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,16 +9244,16 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>52.75718018593754</v>
+        <v>54.86737080601456</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11.55480269731016</v>
+        <v>25.04341006107894</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.12390908451711</v>
+        <v>0.8225951434511225</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>3.55384245798177</v>
+        <v>0.1020485842383657</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3523</v>
+        <v>3224</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>三顧</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>298.7507323101936</v>
+        <v>306.1729769676325</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>16</v>
+        <v>38.4</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,13 +9297,13 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46.68166159971205</v>
+        <v>48.88812647579092</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>13.55921155947915</v>
+        <v>13.88592684037264</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.9769035300117986</v>
+        <v>0.3726678371602096</v>
       </c>
       <c r="K167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.4231434740613766</v>
+        <v>0.2486498962134201</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>3631</v>
+        <v>3680</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>晟楠</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>288.7527822324129</v>
+        <v>298.9365022685526</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>33.8</v>
+        <v>535</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>44.779660517026</v>
+        <v>52.75718018593754</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>13.79524343503752</v>
+        <v>11.55480269731016</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.6159168811199266</v>
+        <v>1.12390908451711</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.0762697627987224</v>
+        <v>3.55384245798177</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>3138</v>
+        <v>3523</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>287.0124064143521</v>
+        <v>298.7507323101936</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>118.5</v>
+        <v>16</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,13 +9403,13 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>30.64604712464101</v>
+        <v>46.68166159971205</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>37.76057758795879</v>
+        <v>13.55921155947915</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.509621354908946</v>
+        <v>0.9769035300117986</v>
       </c>
       <c r="K169" s="2" t="n">
         <v>0</v>
@@ -9421,31 +9421,31 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.4917101423711933</v>
+        <v>-0.4231434740613766</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>3339</v>
+        <v>3631</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>晟楠</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>286.9091224303502</v>
+        <v>288.7527822324129</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>41.25</v>
+        <v>33.8</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,13 +9456,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>38.60479117859478</v>
+        <v>44.779660517026</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>10.6625768880958</v>
+        <v>13.79524343503752</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.6561315411402333</v>
+        <v>0.6159168811199266</v>
       </c>
       <c r="K170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.3274118787105315</v>
+        <v>0.0762697627987224</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>3701</v>
+        <v>3138</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>耀登</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>286.6884538739342</v>
+        <v>287.0124064143521</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>44.8</v>
+        <v>118.5</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>37.9951313415821</v>
+        <v>30.64604712464101</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>33.61373913265754</v>
+        <v>37.76057758795879</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.8568351842742449</v>
+        <v>0.509621354908946</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.1201371791153427</v>
+        <v>-0.4917101423711933</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>3535</v>
+        <v>3339</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>286.2146531636008</v>
+        <v>286.9091224303502</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>113</v>
+        <v>41.25</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,13 +9562,13 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>39.79838098911161</v>
+        <v>38.60479117859478</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>15.43136635444506</v>
+        <v>10.6625768880958</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.8657615231970776</v>
+        <v>0.6561315411402333</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-1.142147013935506</v>
+        <v>-0.3274118787105315</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>3665</v>
+        <v>3701</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>281.7943944802495</v>
+        <v>286.6884538739342</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>1945</v>
+        <v>44.8</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>47.8859379203453</v>
+        <v>37.9951313415821</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>7.708239809126414</v>
+        <v>33.61373913265754</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.6948597711977608</v>
+        <v>0.8568351842742449</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>13.49750381240101</v>
+        <v>0.1201371791153427</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>3287</v>
+        <v>3535</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>廣寰科</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>280.7777329246092</v>
+        <v>286.2146531636008</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>33.4</v>
+        <v>113</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,13 +9668,13 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>50.77928730494293</v>
+        <v>39.79838098911161</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>14.52572406040786</v>
+        <v>15.43136635444506</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.5473557057113737</v>
+        <v>0.8657615231970776</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.1498413306967354</v>
+        <v>-1.142147013935506</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3661</v>
+        <v>3665</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>279.3209942021426</v>
+        <v>281.7943944802495</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>4215</v>
+        <v>1945</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,13 +9721,13 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>47.46488540140581</v>
+        <v>47.8859379203453</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>14.98907162822993</v>
+        <v>7.708239809126414</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>1.143727463806343</v>
+        <v>0.6948597711977608</v>
       </c>
       <c r="K175" s="2" t="n">
         <v>0</v>
@@ -9739,31 +9739,31 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>29.65532516830612</v>
+        <v>13.49750381240101</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>3164</v>
+        <v>3287</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>景岳</t>
+          <t>廣寰科</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>271.4405974913385</v>
+        <v>280.7777329246092</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>16.5</v>
+        <v>33.4</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>54.5987500661274</v>
+        <v>50.77928730494293</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>22.26569786179867</v>
+        <v>14.52572406040786</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.001102512741726</v>
+        <v>0.5473557057113737</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0544880607679231</v>
+        <v>-0.1498413306967354</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3305</v>
+        <v>3661</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>270.1237399805269</v>
+        <v>279.3209942021426</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>136.5</v>
+        <v>4215</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,13 +9827,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>47.13003236050848</v>
+        <v>47.46488540140581</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>16.23641968953885</v>
+        <v>14.98907162822993</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.5184116680292299</v>
+        <v>1.143727463806343</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-1.030268998111572</v>
+        <v>29.65532516830612</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>3693</v>
+        <v>3164</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>營邦</t>
+          <t>景岳</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>269.2388588823781</v>
+        <v>271.4405974913385</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>493.5</v>
+        <v>16.5</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>44.23228017047301</v>
+        <v>54.5987500661274</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>14.61185361024166</v>
+        <v>22.26569786179867</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.6691389755510827</v>
+        <v>1.001102512741726</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>2.192564722748777</v>
+        <v>0.0544880607679231</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3501</v>
+        <v>3305</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>維熹</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>269.1980891559743</v>
+        <v>270.1237399805269</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>41.55</v>
+        <v>136.5</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>50.40475249994027</v>
+        <v>47.13003236050848</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>12.8931544973104</v>
+        <v>16.23641968953885</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.8631964746097465</v>
+        <v>0.5184116680292299</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
@@ -9951,31 +9951,31 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.09420368343003389</v>
+        <v>-1.030268998111572</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>3150</v>
+        <v>3693</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>營邦</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>266.980523408369</v>
+        <v>269.2388588823781</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>19.05</v>
+        <v>493.5</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>49.03930477460509</v>
+        <v>44.23228017047301</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>19.40299638152125</v>
+        <v>14.61185361024166</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.6486077260149278</v>
+        <v>0.6691389755510827</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>0</v>
@@ -10004,31 +10004,31 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.0132337758659469</v>
+        <v>2.192564722748777</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>3289</v>
+        <v>3501</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>宜特</t>
+          <t>維熹</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>266.6944198527069</v>
+        <v>269.1980891559743</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>169</v>
+        <v>41.55</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10039,16 +10039,16 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>48.95375499846074</v>
+        <v>50.40475249994027</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>13.46414411208771</v>
+        <v>12.8931544973104</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>1.467711882366904</v>
+        <v>0.8631964746097465</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L181" s="2" t="n">
         <v>0</v>
@@ -10057,31 +10057,31 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>1.121340944392343</v>
+        <v>0.09420368343003389</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>3576</v>
+        <v>3150</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>263.4916243542167</v>
+        <v>266.980523408369</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>16.85</v>
+        <v>19.05</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10092,13 +10092,13 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>44.97235191105236</v>
+        <v>49.03930477460509</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>11.96745203294676</v>
+        <v>19.40299638152125</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.3677529820828279</v>
+        <v>0.6486077260149278</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>0</v>
@@ -10110,31 +10110,31 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.1333714877485861</v>
+        <v>-0.0132337758659469</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>3207</v>
+        <v>3289</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>耀勝</t>
+          <t>宜特</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>262.1679030085766</v>
+        <v>266.6944198527069</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>63.7</v>
+        <v>169</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,16 +10145,16 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>44.76631314700185</v>
+        <v>48.95375499846074</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>12.88277969222437</v>
+        <v>13.46414411208771</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.2009491618310135</v>
+        <v>1.467711882366904</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.5600656863666139</v>
+        <v>1.121340944392343</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>4137</v>
+        <v>3576</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>麗豐-KY</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>258.6971192577593</v>
+        <v>263.4916243542167</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>96.5</v>
+        <v>16.85</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,13 +10198,13 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>29.51461913189875</v>
+        <v>44.97235191105236</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>25.64693737282193</v>
+        <v>11.96745203294676</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>1.016631689806365</v>
+        <v>0.3677529820828279</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
@@ -10216,31 +10216,31 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-1.649671976462376</v>
+        <v>-0.1333714877485861</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>3686</v>
+        <v>3207</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>達能</t>
+          <t>耀勝</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>254.4511348373156</v>
+        <v>262.1679030085766</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>17.3</v>
+        <v>63.7</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -10251,13 +10251,13 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>51.47340838257615</v>
+        <v>44.76631314700185</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>12.91850975796132</v>
+        <v>12.88277969222437</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.7607052185956609</v>
+        <v>0.2009491618310135</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0330400223036261</v>
+        <v>-0.5600656863666139</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>3232</v>
+        <v>4137</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>麗豐-KY</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>253.9782589378355</v>
+        <v>258.6971192577593</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>22.3</v>
+        <v>96.5</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,13 +10304,13 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>47.37803833664953</v>
+        <v>29.51461913189875</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>20.88558209499732</v>
+        <v>25.64693737282193</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.3700489162248548</v>
+        <v>1.016631689806365</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
@@ -10322,31 +10322,31 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.0913154614280023</v>
+        <v>-1.649671976462376</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>3310</v>
+        <v>3686</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>達能</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>253.5041250140344</v>
+        <v>254.4511348373156</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>68.5</v>
+        <v>17.3</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,16 +10357,16 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>54.68092531204025</v>
+        <v>51.47340838257615</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>24.47148428102188</v>
+        <v>12.91850975796132</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.6368835624470213</v>
+        <v>0.7607052185956609</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L187" s="2" t="n">
         <v>0</v>
@@ -10375,31 +10375,31 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.4224357668421683</v>
+        <v>0.0330400223036261</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>4104</v>
+        <v>3232</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>252.2472045347584</v>
+        <v>253.9782589378355</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>69.7</v>
+        <v>22.3</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,13 +10410,13 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>49.99798541308274</v>
+        <v>47.37803833664953</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>17.34251923784835</v>
+        <v>20.88558209499732</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>1.229865264866278</v>
+        <v>0.3700489162248548</v>
       </c>
       <c r="K188" s="2" t="n">
         <v>0</v>
@@ -10428,31 +10428,31 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.1335790749683005</v>
+        <v>-0.0913154614280023</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>3322</v>
+        <v>3310</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>佳穎</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>249.4430185437984</v>
+        <v>253.5041250140344</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>14.35</v>
+        <v>68.5</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,16 +10463,16 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>51.06728692149422</v>
+        <v>54.68092531204025</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>15.73957870423996</v>
+        <v>24.47148428102188</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>0.5108888327373512</v>
+        <v>0.6368835624470213</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0833206468660997</v>
+        <v>0.4224357668421683</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>3169</v>
+        <v>4104</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>亞信</t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>247.8479293184861</v>
+        <v>252.2472045347584</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>107</v>
+        <v>69.7</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46.63778896826376</v>
+        <v>49.99798541308274</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>12.85788478237765</v>
+        <v>17.34251923784835</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.8190316803467009</v>
+        <v>1.229865264866278</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.3365192266388945</v>
+        <v>0.1335790749683005</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>3434</v>
+        <v>3322</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>哲固</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>246.6120905879268</v>
+        <v>249.4430185437984</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>30.35</v>
+        <v>14.35</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,16 +10569,16 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>51.04566207095974</v>
+        <v>51.06728692149422</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>18.81266760796507</v>
+        <v>15.73957870423996</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.5885216077021561</v>
+        <v>0.5108888327373512</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.0327095073432052</v>
+        <v>-0.0833206468660997</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>3515</v>
+        <v>3169</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>亞信</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>246.3701326009676</v>
+        <v>247.8479293184861</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,16 +10622,16 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>37.09679624172686</v>
+        <v>46.63778896826376</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>16.48815044148311</v>
+        <v>12.85788478237765</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.593283768641902</v>
+        <v>0.8190316803467009</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-3.665347266508711</v>
+        <v>-0.3365192266388945</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>3664</v>
+        <v>3434</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>安瑞-KY</t>
+          <t>哲固</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>240.3532611973132</v>
+        <v>246.6120905879268</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>7.6</v>
+        <v>30.35</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>51.26402638359377</v>
+        <v>51.04566207095974</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>12.24375980150092</v>
+        <v>18.81266760796507</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.6867971060867394</v>
+        <v>0.5885216077021561</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.1372560656756849</v>
+        <v>-0.0327095073432052</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>3531</v>
+        <v>3515</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>先益</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>239.6056935753677</v>
+        <v>246.3701326009676</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>23.25</v>
+        <v>217</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>53.26239723461613</v>
+        <v>37.09679624172686</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>9.977335237983359</v>
+        <v>16.48815044148311</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.2574717990464007</v>
+        <v>0.593283768641902</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>1.313181018358784</v>
+        <v>-3.665347266508711</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>3499</v>
+        <v>3664</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>環天科</t>
+          <t>安瑞-KY</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>234.8953333462216</v>
+        <v>240.3532611973132</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>14.85</v>
+        <v>7.6</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>51.46113865697842</v>
+        <v>51.26402638359377</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>17.11228320511482</v>
+        <v>12.24375980150092</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>1.126492860124297</v>
+        <v>0.6867971060867394</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>0.0572368558385894</v>
+        <v>0.1372560656756849</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>3354</v>
+        <v>3531</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>律勝</t>
+          <t>先益</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>232.8202585145642</v>
+        <v>239.6056935753677</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>27.3</v>
+        <v>23.25</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,16 +10834,16 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>44.26320973067664</v>
+        <v>53.26239723461613</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>14.11008215550391</v>
+        <v>9.977335237983359</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.8535711715003769</v>
+        <v>0.2574717990464007</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.0611871540999776</v>
+        <v>1.313181018358784</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>3593</v>
+        <v>3499</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>力銘</t>
+          <t>環天科</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>232.2902697356189</v>
+        <v>234.8953333462216</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>14.75</v>
+        <v>14.85</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>34.97314432258771</v>
+        <v>51.46113865697842</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>30.62705784438145</v>
+        <v>17.11228320511482</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.9806570821380416</v>
+        <v>1.126492860124297</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0963941820861864</v>
+        <v>0.0572368558385894</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>3467</v>
+        <v>3354</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>台灣精材</t>
+          <t>律勝</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>227.7766433700885</v>
+        <v>232.8202585145642</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>61.1</v>
+        <v>27.3</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,16 +10940,16 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>42.00681032070743</v>
+        <v>44.26320973067664</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>12.52859037580038</v>
+        <v>14.11008215550391</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.7676955297536452</v>
+        <v>0.8535711715003769</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L198" s="2" t="n">
         <v>0</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.5049533101144275</v>
+        <v>0.0611871540999776</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10968,21 +10968,21 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>3432</v>
+        <v>3593</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>力銘</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>217.1607007531163</v>
+        <v>232.2902697356189</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>18.4</v>
+        <v>14.75</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,13 +10993,13 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>48.93119687889156</v>
+        <v>34.97314432258771</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>11.22600731715419</v>
+        <v>30.62705784438145</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>1.222521028865677</v>
+        <v>0.9806570821380416</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.0191741880488</v>
+        <v>-0.0963941820861864</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>3703</v>
+        <v>3467</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>欣陸</t>
+          <t>台灣精材</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>208.5140842851272</v>
+        <v>227.7766433700885</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>20.85</v>
+        <v>61.1</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>43.64321517784531</v>
+        <v>42.00681032070743</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>24.37037288787071</v>
+        <v>12.52859037580038</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.5789978923847579</v>
+        <v>0.7676955297536452</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
@@ -11064,31 +11064,31 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.1178574534056794</v>
+        <v>-0.5049533101144275</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>3325</v>
+        <v>3432</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>旭品</t>
+          <t>台端</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>207.3864396237232</v>
+        <v>217.1607007531163</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>13.4</v>
+        <v>18.4</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>58.29692744604542</v>
+        <v>48.93119687889156</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>18.44196673987523</v>
+        <v>11.22600731715419</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>1.289603814864914</v>
+        <v>1.222521028865677</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>0.09272103948723739</v>
+        <v>0.0191741880488</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>3388</v>
+        <v>3703</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>崇越電</t>
+          <t>欣陸</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>204.1383895247424</v>
+        <v>208.5140842851272</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>20.85</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>39.19007331697208</v>
+        <v>43.64321517784531</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>13.93434902865677</v>
+        <v>24.37037288787071</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.6089997143015724</v>
+        <v>0.5789978923847579</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.1499431348099946</v>
+        <v>-0.1178574534056794</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>3130</v>
+        <v>3325</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>旭品</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>202.4259783464603</v>
+        <v>207.3864396237232</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>221</v>
+        <v>13.4</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>43.18962528515986</v>
+        <v>58.29692744604542</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>16.9401410109828</v>
+        <v>18.44196673987523</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>1.842597834646032</v>
+        <v>1.289603814864914</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.2824307214230711</v>
+        <v>0.09272103948723739</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>3168</v>
+        <v>3388</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>眾福科</t>
+          <t>崇越電</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>188.5071298604816</v>
+        <v>204.1383895247424</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>45.55</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>50.73441303532416</v>
+        <v>39.19007331697208</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>22.28315509046088</v>
+        <v>13.93434902865677</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.5575773262286662</v>
+        <v>0.6089997143015724</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.1318304850004344</v>
+        <v>-0.1499431348099946</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>3338</v>
+        <v>3130</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>泰碩</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>185.2427967507313</v>
+        <v>202.4259783464603</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>72.3</v>
+        <v>221</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,13 +11311,13 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>46.86152171341941</v>
+        <v>43.18962528515986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>13.25551547138227</v>
+        <v>16.9401410109828</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.6496274771263436</v>
+        <v>1.842597834646032</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0</v>
@@ -11329,31 +11329,31 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.2725788447656001</v>
+        <v>-0.2824307214230711</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>3705</v>
+        <v>3168</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>永信</t>
+          <t>眾福科</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>184.2634798271853</v>
+        <v>188.5071298604816</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>54.5</v>
+        <v>45.55</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,13 +11364,13 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>41.80432919046907</v>
+        <v>50.73441303532416</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>28.05283593424572</v>
+        <v>22.28315509046088</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.8846120714276924</v>
+        <v>0.5575773262286662</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.2143293213550801</v>
+        <v>-0.1318304850004344</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>3684</v>
+        <v>3338</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>榮昌</t>
+          <t>泰碩</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>179.8982393069843</v>
+        <v>185.2427967507313</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>54.2</v>
+        <v>72.3</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,13 +11417,13 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>40.36949695293544</v>
+        <v>46.86152171341941</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>19.98446261825276</v>
+        <v>13.25551547138227</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.2867314408657081</v>
+        <v>0.6496274771263436</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
@@ -11435,31 +11435,31 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.3741104988177965</v>
+        <v>-0.2725788447656001</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>3543</v>
+        <v>3705</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>永信</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>168.2298948536126</v>
+        <v>184.2634798271853</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>31.95</v>
+        <v>54.5</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>50.40751039666797</v>
+        <v>41.80432919046907</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>33.67938994515008</v>
+        <v>28.05283593424572</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>1.365642236122416</v>
+        <v>0.8846120714276924</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
@@ -11488,31 +11488,31 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.3022209132192668</v>
+        <v>-0.2143293213550801</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>3666</v>
+        <v>3684</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>光耀</t>
+          <t>榮昌</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>167.7163488380519</v>
+        <v>179.8982393069843</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>24.35</v>
+        <v>54.2</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -11523,13 +11523,13 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>29.36582916320823</v>
+        <v>40.36949695293544</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>19.01347389179056</v>
+        <v>19.98446261825276</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.5917902898039823</v>
+        <v>0.2867314408657081</v>
       </c>
       <c r="K209" s="2" t="n">
         <v>0</v>
@@ -11541,31 +11541,31 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.0783273228119622</v>
+        <v>-0.3741104988177965</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>3632</v>
+        <v>3543</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>研勤</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>153.8939928475233</v>
+        <v>168.2298948536126</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>7.8</v>
+        <v>31.95</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -11576,13 +11576,13 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>41.43328290177887</v>
+        <v>50.40751039666797</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>12.94800244364853</v>
+        <v>33.67938994515008</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>1.369888182353194</v>
+        <v>1.365642236122416</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>0</v>
@@ -11594,31 +11594,31 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.0122159885682644</v>
+        <v>0.3022209132192668</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>3710</v>
+        <v>3666</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>連展投控</t>
+          <t>光耀</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>151.8399790315989</v>
+        <v>167.7163488380519</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>6</v>
+        <v>24.35</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>45.40533855669871</v>
+        <v>29.36582916320823</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>11.57406666835418</v>
+        <v>19.01347389179056</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.6771343628733746</v>
+        <v>0.5917902898039823</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.0195330388922005</v>
+        <v>-0.0783273228119622</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11657,21 +11657,21 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>3713</v>
+        <v>3632</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>新晶投控</t>
+          <t>研勤</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>151.1767407714921</v>
+        <v>153.8939928475233</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,13 +11682,13 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>48.3674412596659</v>
+        <v>41.43328290177887</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>16.30034230119276</v>
+        <v>12.94800244364853</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.8276322172963714</v>
+        <v>1.369888182353194</v>
       </c>
       <c r="K212" s="2" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.0584291735803402</v>
+        <v>-0.0122159885682644</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11710,21 +11710,21 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>4148</v>
+        <v>3710</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>全宇生技-KY</t>
+          <t>連展投控</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>143.2044520112157</v>
+        <v>151.8399790315989</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>30.85</v>
+        <v>6</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,16 +11735,16 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>46.15976629357702</v>
+        <v>45.40533855669871</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>19.00806311643142</v>
+        <v>11.57406666835418</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.8293035788948709</v>
+        <v>0.6771343628733746</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L213" s="2" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.2299737092363916</v>
+        <v>-0.0195330388922005</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11763,21 +11763,21 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>3259</v>
+        <v>3713</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>新晶投控</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>142.6459560779809</v>
+        <v>151.1767407714921</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>16.75</v>
+        <v>15</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,13 +11788,13 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>52.18768518140485</v>
+        <v>48.3674412596659</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>16.33935880242711</v>
+        <v>16.30034230119276</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.9635592327740564</v>
+        <v>0.8276322172963714</v>
       </c>
       <c r="K214" s="2" t="n">
         <v>0</v>
@@ -11806,31 +11806,31 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.0037784521244666</v>
+        <v>-0.0584291735803402</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>3557</v>
+        <v>4148</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>嘉威</t>
+          <t>全宇生技-KY</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>139.3831731412881</v>
+        <v>143.2044520112157</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>26.25</v>
+        <v>30.85</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>51.55393038980453</v>
+        <v>46.15976629357702</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>16.9567334983111</v>
+        <v>19.00806311643142</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.5116759952830972</v>
+        <v>0.8293035788948709</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.0840067031323994</v>
+        <v>0.2299737092363916</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>3447</v>
+        <v>3259</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>展達</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>131.9724003943054</v>
+        <v>142.6459560779809</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>37.5</v>
+        <v>16.75</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>47.38313245907016</v>
+        <v>52.18768518140485</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>14.19093591676553</v>
+        <v>16.33935880242711</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.3986925327751214</v>
+        <v>0.9635592327740564</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
@@ -11912,31 +11912,31 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.1952758571904294</v>
+        <v>-0.0037784521244666</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>4164</v>
+        <v>3557</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>承業醫</t>
+          <t>嘉威</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>125.9513848076226</v>
+        <v>139.3831731412881</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>29.5</v>
+        <v>26.25</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,13 +11947,13 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>48.29721216866417</v>
+        <v>51.55393038980453</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>19.21605632552296</v>
+        <v>16.9567334983111</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.707083251925639</v>
+        <v>0.5116759952830972</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.135686096691267</v>
+        <v>0.0840067031323994</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>3508</v>
+        <v>3447</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>位速</t>
+          <t>展達</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>123.5519832002116</v>
+        <v>131.9724003943054</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>18</v>
+        <v>37.5</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,16 +12000,16 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>40.83629827469598</v>
+        <v>47.38313245907016</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>9.748775791180488</v>
+        <v>14.19093591676553</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.6403918327837295</v>
+        <v>0.3986925327751214</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
         <v>0</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.1089770986333749</v>
+        <v>-0.1952758571904294</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12028,21 +12028,21 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>3540</v>
+        <v>4164</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>曜越</t>
+          <t>承業醫</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>121.5965365154462</v>
+        <v>125.9513848076226</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>25.5</v>
+        <v>29.5</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,16 +12053,16 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>48.51411020702481</v>
+        <v>48.29721216866417</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>14.1451023469854</v>
+        <v>19.21605632552296</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0.472656964503236</v>
+        <v>0.707083251925639</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L219" s="2" t="n">
         <v>0</v>
@@ -12071,31 +12071,31 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.08023140326245461</v>
+        <v>-0.135686096691267</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>3376</v>
+        <v>3508</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>位速</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>115.6239971334009</v>
+        <v>123.5519832002116</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12106,16 +12106,16 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46.45810262860273</v>
+        <v>40.83629827469598</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>15.28004012384518</v>
+        <v>9.748775791180488</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>0.4011957888534783</v>
+        <v>0.6403918327837295</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L220" s="2" t="n">
         <v>0</v>
@@ -12124,31 +12124,31 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.3267001398120017</v>
+        <v>0.1089770986333749</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>3494</v>
+        <v>3540</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>誠研</t>
+          <t>曜越</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>93.34987202727064</v>
+        <v>121.5965365154462</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>7.95</v>
+        <v>25.5</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -12159,16 +12159,16 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>47.16874593276268</v>
+        <v>48.51411020702481</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>9.636974682784585</v>
+        <v>14.1451023469854</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.9116596426373192</v>
+        <v>0.472656964503236</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L221" s="2" t="n">
         <v>0</v>
@@ -12177,62 +12177,168 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.0165173031032209</v>
+        <v>0.08023140326245461</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>新日興</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>115.6239971334009</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>46.45810262860273</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>15.28004012384518</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>0.4011957888534783</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>-0.3267001398120017</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>誠研</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>93.34987202727064</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>47.16874593276268</v>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>9.636974682784585</v>
+      </c>
+      <c r="J223" s="2" t="n">
+        <v>0.9116596426373192</v>
+      </c>
+      <c r="K223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>-0.0165173031032209</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>3272</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>東碩</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D222" s="2" t="n">
+      <c r="C224" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D224" s="2" t="n">
         <v>65.42447550803041</v>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E224" s="2" t="n">
         <v>15.85</v>
       </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H222" s="2" t="n">
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H224" s="2" t="n">
         <v>39.81180548723352</v>
       </c>
-      <c r="I222" s="2" t="n">
+      <c r="I224" s="2" t="n">
         <v>12.90257069050666</v>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J224" s="2" t="n">
         <v>0.836383276684336</v>
       </c>
-      <c r="K222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N222" s="2" t="n">
+      <c r="K224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N224" s="2" t="n">
         <v>-0.025529766174948</v>
       </c>
-      <c r="O222" s="2" t="inlineStr">
+      <c r="O224" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
